--- a/NektarMap.xlsx
+++ b/NektarMap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F95E9C-9EBA-4D1B-9657-A5AE1E0DCF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5964067-B7C6-4705-9808-043AEBEC9A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CFF2691-E43C-4CC8-A4D8-65AD8583F44E}"/>
+    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{9CFF2691-E43C-4CC8-A4D8-65AD8583F44E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -134,9 +134,6 @@
     <t>length (cm)</t>
   </si>
   <si>
-    <t>2,3,4,5,6,1,2</t>
-  </si>
-  <si>
     <t>arteries27</t>
   </si>
   <si>
@@ -153,6 +150,9 @@
   </si>
   <si>
     <t>crop</t>
+  </si>
+  <si>
+    <t>Crop</t>
   </si>
 </sst>
 </file>
@@ -561,6 +561,9 @@
       <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -615,7 +618,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <f>3.9+48.5</f>
@@ -671,9 +674,7 @@
       <c r="C8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="4">
         <f>0.26+0.06+0.57+7.91+3.57+6.89+11.75</f>
         <v>31.01</v>
@@ -747,7 +748,7 @@
         <v>40.159999999999997</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -795,7 +796,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16">
         <f>16+20.5</f>
@@ -821,9 +822,7 @@
       <c r="C17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
+      <c r="D17" s="4"/>
       <c r="E17" s="4">
         <v>21.87</v>
       </c>
@@ -843,7 +842,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <f>6+12</f>
@@ -978,7 +977,7 @@
         <v>39.4</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1004,9 +1003,7 @@
       <c r="C28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="3">
-        <v>4</v>
-      </c>
+      <c r="D28" s="3"/>
       <c r="E28" s="3">
         <v>1.27</v>
       </c>
@@ -1130,7 +1127,7 @@
         <v>21.67</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1167,7 +1164,7 @@
         <v>10.19</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1204,7 +1201,7 @@
         <v>8.6</v>
       </c>
       <c r="F39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1241,7 +1238,7 @@
         <v>15.54</v>
       </c>
       <c r="F41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1286,7 +1283,7 @@
         <v>6.8</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1354,7 +1351,7 @@
         <v>14.5</v>
       </c>
       <c r="C48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -1380,7 +1377,7 @@
         <v>64.06</v>
       </c>
       <c r="F49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1425,7 +1422,7 @@
         <v>5.8</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -1485,7 +1482,7 @@
         <v>64.099999999999994</v>
       </c>
       <c r="F55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">

--- a/NektarMap.xlsx
+++ b/NektarMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5964067-B7C6-4705-9808-043AEBEC9A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696878F0-D30C-4264-B6FF-F7D1CD8BA9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{9CFF2691-E43C-4CC8-A4D8-65AD8583F44E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{9CFF2691-E43C-4CC8-A4D8-65AD8583F44E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -536,16 +536,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F6637A-1E51-4C1A-8376-38D973718918}">
   <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.265625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.265625" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" customWidth="1"/>
+    <col min="5" max="5" width="12.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +565,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -582,7 +582,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -599,7 +599,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -616,7 +616,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>33</v>
       </c>
@@ -634,7 +634,7 @@
         <v>44.62</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -647,7 +647,7 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -664,7 +664,7 @@
         <v>18.97</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -680,7 +680,7 @@
         <v>31.01</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -697,7 +697,7 @@
         <v>21.95</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -714,7 +714,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>12.56</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
@@ -751,7 +751,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -764,7 +764,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -777,7 +777,7 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -794,7 +794,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
@@ -812,7 +812,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -827,7 +827,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -840,7 +840,7 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
         <v>35</v>
       </c>
@@ -858,7 +858,7 @@
         <v>24.12</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>19</v>
       </c>
@@ -875,7 +875,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>20</v>
       </c>
@@ -892,7 +892,7 @@
         <v>19.72</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>21</v>
       </c>
@@ -909,7 +909,7 @@
         <v>44.19</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>22</v>
       </c>
@@ -926,7 +926,7 @@
         <v>25.21</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>23</v>
       </c>
@@ -943,7 +943,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>24</v>
       </c>
@@ -960,7 +960,7 @@
         <v>11.34</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>25</v>
       </c>
@@ -980,7 +980,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -993,7 +993,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>10.029999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>13.72</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>52.99</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>11.96</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>13.53</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>52.88</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>9.61</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>55</v>
       </c>

--- a/NektarMap.xlsx
+++ b/NektarMap.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696878F0-D30C-4264-B6FF-F7D1CD8BA9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F81EBE5-22BD-445D-85A5-873DD62A7BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{9CFF2691-E43C-4CC8-A4D8-65AD8583F44E}"/>
   </bookViews>
@@ -168,7 +168,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -199,6 +199,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -212,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -221,6 +227,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -747,7 +754,7 @@
       <c r="E12">
         <v>40.159999999999997</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="6" t="s">
         <v>37</v>
       </c>
     </row>
@@ -976,7 +983,7 @@
       <c r="E26">
         <v>39.4</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="6" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1126,7 +1133,7 @@
       <c r="E35">
         <v>21.67</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="6" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1163,7 +1170,7 @@
       <c r="E37">
         <v>10.19</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="6" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1200,7 +1207,7 @@
       <c r="E39">
         <v>8.6</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="6" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1237,7 +1244,7 @@
       <c r="E41">
         <v>15.54</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="6" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1376,7 +1383,7 @@
       <c r="E49">
         <v>64.06</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="6" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1481,7 +1488,7 @@
       <c r="E55">
         <v>64.099999999999994</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="6" t="s">
         <v>37</v>
       </c>
     </row>

--- a/NektarMap.xlsx
+++ b/NektarMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F81EBE5-22BD-445D-85A5-873DD62A7BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CBC583-6BC6-43F9-9854-80FBAE58164E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{9CFF2691-E43C-4CC8-A4D8-65AD8583F44E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CFF2691-E43C-4CC8-A4D8-65AD8583F44E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="40">
   <si>
     <t>Nektar ID Number</t>
   </si>
@@ -153,13 +153,16 @@
   </si>
   <si>
     <t>Crop</t>
+  </si>
+  <si>
+    <t>Gotta crop pulmonary!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,8 +170,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,6 +215,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -218,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -228,6 +244,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,17 +559,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F6637A-1E51-4C1A-8376-38D973718918}">
-  <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:K56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.265625" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="23.265625" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" customWidth="1"/>
-    <col min="5" max="5" width="12.3984375" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,7 +589,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -588,8 +605,15 @@
       <c r="E2">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -605,8 +629,13 @@
       <c r="E3">
         <v>0.67</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -622,8 +651,13 @@
       <c r="E4">
         <v>6.7</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>33</v>
       </c>
@@ -640,8 +674,13 @@
       <c r="E5">
         <v>44.62</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -653,8 +692,13 @@
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -670,8 +714,13 @@
       <c r="E7">
         <v>18.97</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -687,7 +736,7 @@
         <v>31.01</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -704,7 +753,7 @@
         <v>21.95</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -721,7 +770,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -738,7 +787,7 @@
         <v>12.56</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -758,7 +807,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -771,7 +820,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -784,7 +833,7 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -801,7 +850,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
@@ -819,7 +868,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -834,7 +883,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -847,7 +896,7 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>35</v>
       </c>
@@ -865,7 +914,7 @@
         <v>24.12</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -882,7 +931,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -899,7 +948,7 @@
         <v>19.72</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -916,7 +965,7 @@
         <v>44.19</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -933,7 +982,7 @@
         <v>25.21</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -950,7 +999,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -967,7 +1016,7 @@
         <v>11.34</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -987,7 +1036,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1000,7 +1049,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1015,7 +1064,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1032,7 +1081,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1049,7 +1098,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1066,7 +1115,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1083,7 +1132,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1100,7 +1149,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1117,7 +1166,7 @@
         <v>10.029999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1137,7 +1186,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1154,7 +1203,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1174,7 +1223,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1191,7 +1240,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1211,7 +1260,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1228,7 +1277,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1248,7 +1297,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1265,7 +1314,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1282,7 +1331,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1299,7 +1348,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1316,7 +1365,7 @@
         <v>13.72</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1333,7 +1382,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1350,7 +1399,7 @@
         <v>52.99</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1367,7 +1416,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1387,7 +1436,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1404,7 +1453,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1421,7 +1470,7 @@
         <v>11.96</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1438,7 +1487,7 @@
         <v>13.53</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1455,7 +1504,7 @@
         <v>52.88</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1472,7 +1521,7 @@
         <v>9.61</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1492,7 +1541,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>

--- a/NektarMap.xlsx
+++ b/NektarMap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CBC583-6BC6-43F9-9854-80FBAE58164E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D4E028-3A1A-43AF-B260-B40E5E222425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CFF2691-E43C-4CC8-A4D8-65AD8583F44E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{9CFF2691-E43C-4CC8-A4D8-65AD8583F44E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="40">
   <si>
     <t>Nektar ID Number</t>
   </si>
@@ -560,16 +560,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F6637A-1E51-4C1A-8376-38D973718918}">
   <dimension ref="A1:K56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.265625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.265625" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" customWidth="1"/>
+    <col min="5" max="5" width="12.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +589,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -613,7 +613,7 @@
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -635,7 +635,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -657,7 +657,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>33</v>
       </c>
@@ -680,7 +680,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -698,7 +698,7 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -720,7 +720,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -736,7 +736,7 @@
         <v>31.01</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -753,7 +753,7 @@
         <v>21.95</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -770,7 +770,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -787,7 +787,7 @@
         <v>12.56</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
@@ -807,7 +807,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -820,7 +820,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -833,7 +833,7 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -850,7 +850,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
@@ -868,7 +868,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -883,7 +883,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -896,7 +896,7 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
         <v>35</v>
       </c>
@@ -914,7 +914,7 @@
         <v>24.12</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>19</v>
       </c>
@@ -931,7 +931,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>20</v>
       </c>
@@ -948,7 +948,7 @@
         <v>19.72</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>21</v>
       </c>
@@ -965,7 +965,7 @@
         <v>44.19</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>22</v>
       </c>
@@ -982,7 +982,7 @@
         <v>25.21</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>23</v>
       </c>
@@ -999,7 +999,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>11.34</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1049,7 +1049,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>10.029999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>13.72</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>52.99</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1452,8 +1452,11 @@
       <c r="E50">
         <v>53.1</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F50" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1470,7 +1473,7 @@
         <v>11.96</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1487,7 +1490,7 @@
         <v>13.53</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1504,7 +1507,7 @@
         <v>52.88</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1521,7 +1524,7 @@
         <v>9.61</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1541,7 +1544,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1556,6 +1559,9 @@
       </c>
       <c r="E56">
         <v>53.24</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
